--- a/data/trans_dic/IQ2601_R2-Edad-trans_dic.xlsx
+++ b/data/trans_dic/IQ2601_R2-Edad-trans_dic.xlsx
@@ -533,7 +533,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -541,7 +541,7 @@
       <c r="F1" s="3" t="n"/>
       <c r="G1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="H1" s="3" t="n"/>
@@ -649,42 +649,42 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>76,5%</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>54,98%</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>59,97%</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>84,77%</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
           <t>76,07%</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="H4" s="2" t="inlineStr">
         <is>
           <t>48,37%</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="I4" s="2" t="inlineStr">
         <is>
           <t>51,95%</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>73,08%</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>76,5%</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>54,98%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>59,97%</t>
-        </is>
-      </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>81,03%</t>
+          <t>72,05%</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -704,7 +704,7 @@
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>77,2%</t>
+          <t>78,08%</t>
         </is>
       </c>
     </row>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>69,0; 83,05</t>
+          <t>69,3; 82,22</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>41,24; 55,33</t>
+          <t>46,31; 61,77</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>44,21; 58,79</t>
+          <t>52,43; 66,45</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>50,86; 89,77</t>
+          <t>67,06; 96,02</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>69,51; 82,42</t>
+          <t>68,49; 82,64</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>47,31; 62,65</t>
+          <t>41,75; 55,74</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>52,12; 67,18</t>
+          <t>44,32; 58,98</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>57,19; 94,48</t>
+          <t>48,04; 88,53</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>71,06; 80,79</t>
+          <t>71,81; 81,0</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>46,09; 56,45</t>
+          <t>46,1; 56,81</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>50,72; 60,86</t>
+          <t>50,69; 61,42</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>63,15; 89,03</t>
+          <t>63,95; 89,51</t>
         </is>
       </c>
     </row>
@@ -789,42 +789,42 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>74,55%</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>55,82%</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>64,95%</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>67,78%</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
           <t>73,99%</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="H6" s="2" t="inlineStr">
         <is>
           <t>59,83%</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="I6" s="2" t="inlineStr">
         <is>
           <t>65,35%</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>74,36%</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>74,55%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>55,82%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>64,95%</t>
-        </is>
-      </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>67,98%</t>
+          <t>71,79%</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -844,7 +844,7 @@
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>70,75%</t>
+          <t>69,53%</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>69,54; 78,07</t>
+          <t>70,25; 79,05</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>54,2; 65,07</t>
+          <t>51,02; 61,32</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>60,06; 70,39</t>
+          <t>60,28; 69,58</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>62,46; 85,5</t>
+          <t>54,39; 78,16</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>69,75; 78,71</t>
+          <t>69,47; 78,78</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>50,18; 61,06</t>
+          <t>54,98; 65,7</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>59,99; 69,08</t>
+          <t>60,16; 70,72</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>55,06; 77,78</t>
+          <t>59,94; 82,55</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>70,83; 77,1</t>
+          <t>70,95; 76,93</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>53,76; 61,03</t>
+          <t>54,18; 61,25</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>61,74; 68,64</t>
+          <t>61,58; 68,5</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>62,01; 78,58</t>
+          <t>60,06; 77,23</t>
         </is>
       </c>
     </row>
@@ -929,42 +929,42 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>66,87%</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>52,12%</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>66,94%</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>74,82%</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
           <t>68,18%</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="H8" s="2" t="inlineStr">
         <is>
           <t>48,32%</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
+      <c r="I8" s="2" t="inlineStr">
         <is>
           <t>68,4%</t>
         </is>
       </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>72,71%</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>66,87%</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>52,12%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>66,94%</t>
-        </is>
-      </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>75,65%</t>
+          <t>70,86%</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>74,42%</t>
+          <t>73,16%</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>61,37; 75,02</t>
+          <t>60,12; 72,69</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>41,63; 55,08</t>
+          <t>45,37; 58,35</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>62,77; 74,06</t>
+          <t>61,68; 72,45</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>58,43; 84,22</t>
+          <t>62,41; 84,51</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>59,95; 73,1</t>
+          <t>61,0; 74,46</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>45,67; 58,63</t>
+          <t>42,07; 55,17</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>61,17; 72,31</t>
+          <t>62,77; 73,4</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>64,54; 84,51</t>
+          <t>55,87; 81,68</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>62,76; 72,03</t>
+          <t>62,91; 71,64</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>45,36; 55,22</t>
+          <t>45,21; 54,93</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>62,66; 71,25</t>
+          <t>63,13; 71,37</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>65,66; 82,24</t>
+          <t>63,22; 80,36</t>
         </is>
       </c>
     </row>
@@ -1069,42 +1069,42 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>47,38%</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>32,36%</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>63,52%</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>73,6%</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
           <t>55,84%</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="H10" s="2" t="inlineStr">
         <is>
           <t>49,25%</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
+      <c r="I10" s="2" t="inlineStr">
         <is>
           <t>66,19%</t>
         </is>
       </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>63,66%</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>47,38%</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>32,36%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>63,52%</t>
-        </is>
-      </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>72,84%</t>
+          <t>63,32%</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1124,7 +1124,7 @@
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>69,03%</t>
+          <t>69,14%</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>50,09; 60,93</t>
+          <t>41,76; 52,91</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>42,55; 55,56</t>
+          <t>26,73; 38,01</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>59,78; 72,17</t>
+          <t>57,03; 69,85</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>52,5; 74,72</t>
+          <t>61,85; 82,48</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>42,26; 52,82</t>
+          <t>49,37; 60,83</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>27,33; 38,3</t>
+          <t>42,62; 55,17</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>56,66; 69,17</t>
+          <t>59,48; 72,17</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>62,35; 82,31</t>
+          <t>51,37; 74,26</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>47,63; 55,52</t>
+          <t>47,44; 55,03</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>36,35; 44,49</t>
+          <t>36,14; 44,73</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>60,43; 68,92</t>
+          <t>60,18; 68,88</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>60,96; 76,92</t>
+          <t>61,85; 76,41</t>
         </is>
       </c>
     </row>
@@ -1209,42 +1209,42 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>65,39%</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>49,06%</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>64,33%</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>73,38%</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
           <t>67,86%</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="H12" s="2" t="inlineStr">
         <is>
           <t>52,5%</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="I12" s="2" t="inlineStr">
         <is>
           <t>64,06%</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>69,68%</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>65,39%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>49,06%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>64,33%</t>
-        </is>
-      </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>73,13%</t>
+          <t>68,06%</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
@@ -1264,7 +1264,7 @@
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>71,66%</t>
+          <t>71,05%</t>
         </is>
       </c>
     </row>
@@ -1277,62 +1277,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>65,02; 70,61</t>
+          <t>62,22; 68,07</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>49,05; 55,47</t>
+          <t>45,83; 52,09</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>61,16; 66,79</t>
+          <t>61,19; 67,41</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>62,91; 75,68</t>
+          <t>67,04; 78,97</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>62,17; 67,92</t>
+          <t>65,16; 70,86</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>45,69; 52,07</t>
+          <t>49,44; 55,67</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>61,56; 67,25</t>
+          <t>60,93; 66,86</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>67,0; 79,36</t>
+          <t>61,36; 74,37</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>64,67; 68,55</t>
+          <t>64,54; 68,67</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>48,65; 53,02</t>
+          <t>48,66; 53,14</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>61,99; 66,26</t>
+          <t>62,25; 66,12</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>67,07; 75,65</t>
+          <t>66,6; 75,37</t>
         </is>
       </c>
     </row>
@@ -1393,7 +1393,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -1401,7 +1401,7 @@
       <c r="F1" s="3" t="n"/>
       <c r="G1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="H1" s="3" t="n"/>
@@ -1509,42 +1509,42 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>121</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>92</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>106</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
           <t>105</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="H4" s="2" t="inlineStr">
         <is>
           <t>92</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="I4" s="2" t="inlineStr">
         <is>
           <t>101</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
+      <c r="J4" s="2" t="inlineStr">
         <is>
           <t>19</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>121</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>92</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>106</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>25</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -1577,42 +1577,42 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>81045</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>65191</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>69959</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>9466</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
           <t>68658</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="H5" s="2" t="inlineStr">
         <is>
           <t>60213</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
+      <c r="I5" s="2" t="inlineStr">
         <is>
           <t>62770</t>
         </is>
       </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>9746</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>81045</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>65191</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>69959</t>
-        </is>
-      </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>11595</t>
+          <t>8912</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -1632,7 +1632,7 @@
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>21342</t>
+          <t>18378</t>
         </is>
       </c>
     </row>
@@ -1645,62 +1645,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>62282; 74964</t>
+          <t>73422; 87116</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>51334; 68872</t>
+          <t>54916; 73250</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>53420; 71036</t>
+          <t>61164; 77520</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>6782; 11972</t>
+          <t>7488; 10721</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>73640; 87327</t>
+          <t>61816; 74591</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>56098; 74283</t>
+          <t>51962; 69377</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>60796; 78364</t>
+          <t>53548; 71262</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>8184; 13520</t>
+          <t>5942; 10951</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>139433; 158519</t>
+          <t>140894; 158932</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>112032; 137212</t>
+          <t>112036; 138065</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>120445; 144534</t>
+          <t>120375; 145863</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>17459; 24615</t>
+          <t>15051; 21068</t>
         </is>
       </c>
     </row>
@@ -1717,42 +1717,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>283</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>212</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>249</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>45</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
           <t>280</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="H7" s="2" t="inlineStr">
         <is>
           <t>204</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
+      <c r="I7" s="2" t="inlineStr">
         <is>
           <t>219</t>
         </is>
       </c>
-      <c r="F7" s="2" t="inlineStr">
+      <c r="J7" s="2" t="inlineStr">
         <is>
           <t>46</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>283</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>212</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>249</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>45</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
@@ -1785,42 +1785,42 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>189172</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>150141</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>167598</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>26760</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
           <t>187021</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="H8" s="2" t="inlineStr">
         <is>
           <t>140922</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
+      <c r="I8" s="2" t="inlineStr">
         <is>
           <t>137578</t>
         </is>
       </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>25534</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>189172</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>150141</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>167598</t>
-        </is>
-      </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>30430</t>
+          <t>21967</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -1840,7 +1840,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>55965</t>
+          <t>48727</t>
         </is>
       </c>
     </row>
@@ -1853,62 +1853,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>175769; 197317</t>
+          <t>178272; 200582</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>127660; 153269</t>
+          <t>137249; 164959</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>126439; 148192</t>
+          <t>155566; 179551</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>21448; 29360</t>
+          <t>21473; 30855</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>176986; 199726</t>
+          <t>175579; 199110</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>134967; 164249</t>
+          <t>129491; 154747</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>154800; 178274</t>
+          <t>126637; 148881</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>24647; 34818</t>
+          <t>18342; 25260</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>358746; 390500</t>
+          <t>359376; 389670</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>271228; 307939</t>
+          <t>273346; 309034</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>289302; 321619</t>
+          <t>288541; 320977</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>49055; 62160</t>
+          <t>42086; 54124</t>
         </is>
       </c>
     </row>
@@ -1925,42 +1925,42 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>141</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>119</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>177</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>46</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
           <t>129</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="H10" s="2" t="inlineStr">
         <is>
           <t>110</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
+      <c r="I10" s="2" t="inlineStr">
         <is>
           <t>185</t>
         </is>
       </c>
-      <c r="F10" s="2" t="inlineStr">
+      <c r="J10" s="2" t="inlineStr">
         <is>
           <t>37</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>141</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>119</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>177</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>46</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1993,42 +1993,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>94633</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>82646</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>126230</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>39873</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
           <t>86968</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="H11" s="2" t="inlineStr">
         <is>
           <t>75590</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
+      <c r="I11" s="2" t="inlineStr">
         <is>
           <t>129205</t>
         </is>
       </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>29091</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>94633</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>82646</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>126230</t>
-        </is>
-      </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>42300</t>
+          <t>27249</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
@@ -2048,7 +2048,7 @@
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>71391</t>
+          <t>67123</t>
         </is>
       </c>
     </row>
@@ -2061,62 +2061,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>78282; 95684</t>
+          <t>85075; 102872</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>65131; 86170</t>
+          <t>71940; 92519</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>118576; 139901</t>
+          <t>116305; 136623</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>23378; 33693</t>
+          <t>33262; 45036</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>84837; 103441</t>
+          <t>77801; 94967</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>72420; 92969</t>
+          <t>65819; 86303</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>115350; 136351</t>
+          <t>118566; 138659</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>36090; 47256</t>
+          <t>21483; 31409</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>168863; 193808</t>
+          <t>169277; 192758</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>142893; 173942</t>
+          <t>142409; 173030</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>236506; 268952</t>
+          <t>238305; 269415</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>62986; 78886</t>
+          <t>58007; 73731</t>
         </is>
       </c>
     </row>
@@ -2133,42 +2133,42 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>146</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>88</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>149</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>69</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
           <t>160</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="H13" s="2" t="inlineStr">
         <is>
           <t>119</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
+      <c r="I13" s="2" t="inlineStr">
         <is>
           <t>164</t>
         </is>
       </c>
-      <c r="F13" s="2" t="inlineStr">
+      <c r="J13" s="2" t="inlineStr">
         <is>
           <t>54</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>146</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>88</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>149</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>69</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
@@ -2201,42 +2201,42 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>97623</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>58236</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>110561</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>54779</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
           <t>108391</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="H14" s="2" t="inlineStr">
         <is>
           <t>84384</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
+      <c r="I14" s="2" t="inlineStr">
         <is>
           <t>114713</t>
         </is>
       </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>34612</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>97623</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>58236</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>110561</t>
-        </is>
-      </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>55923</t>
+          <t>36177</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -2256,7 +2256,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>90535</t>
+          <t>90956</t>
         </is>
       </c>
     </row>
@@ -2269,62 +2269,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>97223; 118269</t>
+          <t>86044; 109015</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>72898; 95199</t>
+          <t>48099; 68408</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>103593; 125072</t>
+          <t>99260; 121572</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>28546; 40624</t>
+          <t>46030; 61387</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>87079; 108827</t>
+          <t>95829; 118073</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>49184; 68927</t>
+          <t>73027; 94530</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>98622; 120381</t>
+          <t>103082; 125072</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>47871; 63194</t>
+          <t>29352; 42429</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>190575; 222175</t>
+          <t>189830; 220196</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>127700; 156295</t>
+          <t>126965; 157140</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>209898; 239390</t>
+          <t>209045; 239242</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>79947; 100876</t>
+          <t>81374; 100520</t>
         </is>
       </c>
     </row>
@@ -2341,42 +2341,42 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>691</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>511</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>681</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>185</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
           <t>674</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="H16" s="2" t="inlineStr">
         <is>
           <t>525</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
+      <c r="I16" s="2" t="inlineStr">
         <is>
           <t>669</t>
         </is>
       </c>
-      <c r="F16" s="2" t="inlineStr">
+      <c r="J16" s="2" t="inlineStr">
         <is>
           <t>156</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>691</t>
-        </is>
-      </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>511</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>681</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>185</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
@@ -2409,42 +2409,42 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>462474</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>356214</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>474348</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>130878</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
           <t>451037</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="H17" s="2" t="inlineStr">
         <is>
           <t>361108</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
+      <c r="I17" s="2" t="inlineStr">
         <is>
           <t>444266</t>
         </is>
       </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>98984</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
-        <is>
-          <t>462474</t>
-        </is>
-      </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>356214</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>474348</t>
-        </is>
-      </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>140248</t>
+          <t>94305</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
@@ -2464,7 +2464,7 @@
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>239232</t>
+          <t>225183</t>
         </is>
       </c>
     </row>
@@ -2477,62 +2477,62 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>432164; 469291</t>
+          <t>440089; 481463</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>337344; 381526</t>
+          <t>332768; 378199</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>424179; 463217</t>
+          <t>451187; 497019</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>89370; 107503</t>
+          <t>119578; 140854</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>439742; 480392</t>
+          <t>433101; 470992</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>331716; 378087</t>
+          <t>340065; 382882</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>453926; 495865</t>
+          <t>422565; 463696</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>128483; 152196</t>
+          <t>85022; 103047</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>887289; 940472</t>
+          <t>885396; 942134</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>687891; 749600</t>
+          <t>687930; 751363</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>887063; 948036</t>
+          <t>890646; 946107</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>223897; 252531</t>
+          <t>211054; 238878</t>
         </is>
       </c>
     </row>
